--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.32333</v>
+        <v>16.75073</v>
       </c>
       <c r="D2" t="n">
-        <v>16.36723</v>
+        <v>16.52168</v>
       </c>
       <c r="E2" t="n">
-        <v>16.55322</v>
+        <v>16.72765</v>
       </c>
       <c r="F2" t="n">
-        <v>42.62663</v>
+        <v>41.54542</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05032</v>
+        <v>0.04983</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79853</v>
+        <v>1.82385</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.73002</v>
+        <v>16.83137</v>
       </c>
       <c r="D3" t="n">
-        <v>16.37042</v>
+        <v>16.56343</v>
       </c>
       <c r="E3" t="n">
-        <v>16.8386</v>
+        <v>16.78696</v>
       </c>
       <c r="F3" t="n">
-        <v>41.82804</v>
+        <v>42.40521</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04897</v>
+        <v>0.05008</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79031</v>
+        <v>1.78675</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.51697</v>
+        <v>16.77055</v>
       </c>
       <c r="D4" t="n">
-        <v>16.2364</v>
+        <v>16.53947</v>
       </c>
       <c r="E4" t="n">
-        <v>16.74338</v>
+        <v>16.62621</v>
       </c>
       <c r="F4" t="n">
-        <v>42.34988</v>
+        <v>42.38889</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05016</v>
+        <v>0.0493</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82564</v>
+        <v>1.80913</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.55678</v>
+        <v>16.62986</v>
       </c>
       <c r="D6" t="n">
-        <v>16.21603</v>
+        <v>15.9444</v>
       </c>
       <c r="E6" t="n">
-        <v>16.10606</v>
+        <v>16.05995</v>
       </c>
       <c r="F6" t="n">
-        <v>21.50178</v>
+        <v>21.77983</v>
       </c>
       <c r="G6" t="n">
-        <v>33.90611</v>
+        <v>33.47064</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.39276</v>
+        <v>16.65362</v>
       </c>
       <c r="D7" t="n">
-        <v>15.8767</v>
+        <v>15.59973</v>
       </c>
       <c r="E7" t="n">
-        <v>16.40219</v>
+        <v>16.48366</v>
       </c>
       <c r="F7" t="n">
-        <v>21.69095</v>
+        <v>21.5678</v>
       </c>
       <c r="G7" t="n">
-        <v>34.67238</v>
+        <v>33.7257</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.61285</v>
+        <v>16.40826</v>
       </c>
       <c r="D8" t="n">
-        <v>15.84381</v>
+        <v>15.72111</v>
       </c>
       <c r="E8" t="n">
-        <v>16.4223</v>
+        <v>16.3411</v>
       </c>
       <c r="F8" t="n">
-        <v>21.63007</v>
+        <v>21.60619</v>
       </c>
       <c r="G8" t="n">
-        <v>33.75281</v>
+        <v>34.31073</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5948099999999999</v>
+        <v>0.60361</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1248</v>
+        <v>1.09501</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.59988</v>
+        <v>0.61261</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11129</v>
+        <v>1.09798</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60692</v>
+        <v>0.60854</v>
       </c>
       <c r="D12" t="n">
-        <v>1.14467</v>
+        <v>1.11767</v>
       </c>
     </row>
   </sheetData>
